--- a/daily_matches/job_matches_2026-09-02.xlsx
+++ b/daily_matches/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>AI Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Docker, CI/CD, Git, Databricks, PySpark</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Redshift, BigQuery, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2046c40f9b4630</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bc87d8d4b72fa4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Docker, CI/CD, Git, Databricks, PySpark</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5613eeda948d152d</t>
+          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Docker, CI/CD, Git, Databricks, PySpark</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d82f72b04a6199</t>
+          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Docker, CI/CD, Git, Databricks, PySpark</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10720ff0a4de8cf4</t>
+          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer -Neo4j / Knowledge Graph</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, Docker, Kubernetes, Terraform</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205421f939f9f6af</t>
+          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
+          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Centric Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1350eabc1a8ccc3f</t>
+          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, PostgreSQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642d9d492b002566</t>
+          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Automation Engineer with AI</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, Glue, Docker, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6890c54510ac16b</t>
+          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I – Supply Chain</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Git, Python</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30519bbbe22dc7f2</t>
+          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (B2B Scores)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,277 +881,277 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, S3, Glue, MLflow, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3921b775f4bfb3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, S3, Glue, MLflow, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b5584b1a87e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, S3, Glue, MLflow, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d0ed205376fb17</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, S3, Glue, MLflow, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d05282c79331ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, S3, Glue, MLflow, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a129774c3b6c3e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, S3, Glue, MLflow, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee890dc40655c32</t>
+          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Goal Family of Companies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd32aca13a2489e</t>
+          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Prompt Engineering, Git, Kafka, PostgreSQL, MongoDB, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fea1e62ccbc4440</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Systems &amp; AI Integration Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Oshkosh Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768d3e65308e16d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Software Development &amp; Engineering</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20d43da61d62828</t>
+          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python, SQL</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
+          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Terraform, Git, NoSQL, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
+          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
+          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (React/Java) Web applications</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, S3, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7143123bda142ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Agentic Data Engineer (IC3)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Snowflake, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
+          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineering Trainee</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BLACKBUCK iNSIGHTS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2effc5ea9fcdc2e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Java</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
+          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior .NET Solutions Developer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf14adbbc003139</t>
+          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be26e9957dff2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e9dce9e97399ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QA Automation Developer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332c271f6092f087</t>
+          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer – .NET</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd6ef92dcd7932f7</t>
+          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI/ML Cloud Consultant</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vertical Relevance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, S3, Glue, Git, Hadoop, Python, R</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=056ccc4702223232</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (HYBRID)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C-4 Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4d02012d03960d</t>
+          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java/Azure Developer - Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb5571d0aff35a1</t>
+          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Samaritan's Purse</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boone, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7413a2bb2b6f771</t>
+          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Generative AI, Jenkins, Git, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c38442e5d65cd42</t>
+          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java/Azure Developer - Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3081db7591ba15</t>
+          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineering Intern (Summer 2027)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Clarios</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Snowflake, Databricks, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb282e941afcd4c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sound Income Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad527db0a144ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Agentic Engineer (IC2)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e3d407190b9631</t>
+          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist — Global Services Insights &amp; Analytics, Commercial Banking - Sr. Associate</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, Databricks, Hadoop, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ef56a9b6c6e7952</t>
+          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3080ab4c5c616e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc04b733aa013d08</t>
+          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- New York, NY</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bfccd6fd6ae1824</t>
+          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- New York, NY</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496c21aa2cdc5581</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6fe7ba52ec0769</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Python Data Engineer - SAS Migration</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Data Lake, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Gemini, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15964ce1387afdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Python Data Engineer - SAS Migration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>WIS International</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Data Lake, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Synapse, Git, Databricks, Kafka, Hadoop, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a290ff29f48d81c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b49079cb03df4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java</t>
+          <t>Data Lake, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60be561ca0036517</t>
+          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90aaf8206a988ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=20452cc6c3df4f7c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, Git, Snowflake, Databricks, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,77 +2421,1267 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf90b114f5442003</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Internship, Charging Data Modeling, Machine Learning Engineer (Winter/Spring 2027)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Git, Hadoop, NoSQL, Python, SQL, R, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Dataflow, CI/CD, Git, Snowflake, BigQuery, Redshift, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcc4ea2784764f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Advisor R&amp;D</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Elanco</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lighthouse Document Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Kubernetes, CI/CD, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13c947aa23b732f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Operations</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b68f3d8db0a91ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Steelcase</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Redshift, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Redshift</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SWE &amp; App Arch Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, Docker, Kubernetes, Apache Airflow, Terraform, Git, Snowflake, Databricks, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>US Foods</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Rosemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Jenkins, Git, Snowflake, Kafka, MySQL, Tableau</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI &amp; Analytics Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise | HPE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddc6f7b22c3923b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Transformation Engineer SADA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Git, BigQuery, PostgreSQL, MySQL, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b0588d3c8970130</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Neumo Holdings LLC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>S3, Glue, Athena, Redshift, CI/CD, Redshift, PostgreSQL, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pioneering Evolution</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Child Mind Institute</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Kubernetes, Terraform, Git, NoSQL, Polars, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Westchester, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Git, Hadoop, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Raritan, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer - Go, Python, AWS, Kubernetes/EKS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PortX</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Mercer Island, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Copilot, S3, EC2, Docker, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6869de75829061a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Performance Engineer- JMeter, JavaScript - Remote</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Maximus</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bef4a1587d4ea493</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Engineer - IVR</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28242c11e5b03aad</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Engineer - IVR</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fefdb8c2ca1ff0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Engineer - IVR</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5669473b69f8dfc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Engineer - IVR</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1c5154caded21eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AI Analyst - Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Photon</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfb485445c6b1224</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Owens &amp; Minor</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Glen Allen, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, BigQuery, PySpark, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4aeda45ddcc9276</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tango Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4597a66e729c8507</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Databricks Architect</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>S3, Terraform, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Scientist II - Advanced Analytics</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Novo Nordisk, Inc.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Plainsboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef233fd5c7a57774</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Jr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Climavision</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ffa078439d97db5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BI Developer/ Analyst</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Diversified Gas &amp; Oil</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Cortex, Dataflow, Snowflake, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e30ffff7d49182ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Scientist, Customer Success</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Databricks, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bec4e796b610ab57</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Addressing Team</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
         <v>10</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Databricks, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29da06a98a847fda</t>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kafka, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11562920d71748d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Engineer (Knowledge Graph)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>VeeRteq Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Apache Airflow, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior GRC Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cc2b2627eea8568</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Index Analytics LLC</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Windsor Mill, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d02c9c5cae4d743b</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Digital &amp; IT Intern, Analyst, Manufacturing AI/ML - Summer 2027</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Corning</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c1d6fb9f91a34d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DevOps Engineer – Azure Platform</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38ac80eca36c370b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-02.xlsx
+++ b/daily_matches/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Managing Consultant, Databricks Engineer - Richmond</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Copilot, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,172 +496,172 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
+          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fbdc7437ccf93a</t>
+          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer – CircleCard Platform</t>
+          <t>Software Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Keras, Git, Kafka, Hadoop, Tableau, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf78b0dea5c3485</t>
+          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Production Support Engineering PMTS</t>
+          <t>Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Holland America Line</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, PySpark, PostgreSQL, MySQL, Python</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, S3, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
+          <t>https://www.indeed.com/viewjob?jk=b2af3e5ff2c1802d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer Senior - Mortgage Platforms</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Crunchyroll</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, PyTorch, XGBoost, LightGBM, Tableau, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
+          <t>https://www.indeed.com/viewjob?jk=4cceffb7519ddae1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4116746ecbb0a15</t>
+          <t>https://www.indeed.com/viewjob?jk=cf506201dbac0882</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II - Reliability Engineering Tooling (Remote)</t>
+          <t>Content Engineer II (E6175)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>IEEE Corporate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
+          <t>S3, EC2, Docker, CI/CD, Jenkins, Git, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375bc8995e545ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3f922995d21c0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Scientist III, Ads Optimization &amp; Automation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, BigQuery, Python, R, Scala</t>
+          <t>RAG, S3, Data Lake, Snowflake, Databricks, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6970a989d993f1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Gen AI Developer- Hybrid/Client Site</t>
+          <t>Consultants</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TransUnion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Git, MongoDB, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, PySpark, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fb566323322d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=b35751eeb1fbcd74</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Senior Engineer - AI-Driven Workflows</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, Synapse, Git, Snowflake, Databricks, Redshift, Kafka, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
+          <t>https://www.indeed.com/viewjob?jk=ea87924e59be0176</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>PFM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c46961330ff6e8b3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aspire General Insurance Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7496c850df233a51</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9e03da388871ac</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Application Engineer – AI-Accelerated Development</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allruva Technology Services</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Terraform, Git, SQL, R, Java, Optimization</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459a810d87d48590</t>
+          <t>https://www.indeed.com/viewjob?jk=984c16ff44f344c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (AWS)</t>
+          <t>Senior Core Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
+          <t>https://www.indeed.com/viewjob?jk=c5899c6b78ccd353</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Senior Core Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,139 +976,139 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, Synapse, Snowflake, Databricks, Redshift, Kafka, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
+          <t>https://www.indeed.com/viewjob?jk=192d7298c1dbe48c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>C&amp;W Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
+          <t>https://www.indeed.com/viewjob?jk=21e432297bb03d47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Overseas Contractor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, S3, Glue, MLflow, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cadf6f11232240c</t>
+          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Engineer, Dev Ops</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Samaritan's Purse</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boone, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f5c18ddad1e57c</t>
+          <t>https://www.indeed.com/viewjob?jk=475b5911e2c343f2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cyber Security Engineer - Automation, Data Center &amp; Networking Security</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kaseya</t>
+          <t>Latitude AI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Copilot, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Terraform, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06f318922c7f8af</t>
+          <t>https://www.indeed.com/viewjob?jk=a2d52ae75da259a3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer - Reliability</t>
+          <t>Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Data Lake, CI/CD, Terraform, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Developer – AI Native Engineering</t>
+          <t>Data Scientist - Supply Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,52 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd16e0ee123efaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Flexera</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, MySQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61ca618a0f0d4d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=4920dc6667911d73</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-02.xlsx
+++ b/daily_matches/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Richmond</t>
+          <t>Artificial Intelligence / Machine Learning Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copilot, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, spaCy, OpenCV, YOLO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
+          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
+          <t>Senior Java Backend Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Kafka, Hadoop, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
+          <t>https://www.indeed.com/viewjob?jk=76cf49dceb0f513c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Data Engineer/Data Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Keras, Git, Kafka, Hadoop, Tableau, Python</t>
+          <t>TensorFlow, PyTorch, Git, Snowflake, Databricks, Kafka, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer, AI/ML</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Holland America Line</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, S3, CI/CD, Git, Snowflake</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Keras, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2af3e5ff2c1802d</t>
+          <t>https://www.indeed.com/viewjob?jk=b38b2d7dd112b433</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Engineer Technology</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Crunchyroll</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, PyTorch, XGBoost, LightGBM, Tableau, Matplotlib, Python</t>
+          <t>S3, Glue, Redshift, Kinesis, CI/CD, Redshift, PySpark, Kafka, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cceffb7519ddae1</t>
+          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Dask</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf506201dbac0882</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bc14828ef1e67f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Content Engineer II (E6175)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IEEE Corporate</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Jenkins, Git, MySQL, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Dask</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3f922995d21c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1988c96da6897747</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Snowflake, Databricks, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, AKS, CI/CD, GitHub Actions, Git, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
+          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consultants</t>
+          <t>NoSQL Database Engineer || Onsite</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TransUnion</t>
+          <t>Ukund</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, PySpark, PostgreSQL, MySQL, Python</t>
+          <t>Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35751eeb1fbcd74</t>
+          <t>https://www.indeed.com/viewjob?jk=9314bc9cfb51fe1b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI-Driven Workflows</t>
+          <t>APPLICATION DEVELOPER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Atos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea87924e59be0176</t>
+          <t>https://www.indeed.com/viewjob?jk=88b7d6cdbfaa32a7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Full-Stack Engineer</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PFM</t>
+          <t>Indicium AI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, SQL, R</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46961330ff6e8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a8eb7066c5357ce7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Penguin Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, MLflow, Docker, Kubernetes, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9e03da388871ac</t>
+          <t>https://www.indeed.com/viewjob?jk=999a52875fb68380</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,102 +916,102 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=984c16ff44f344c1</t>
+          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Core Infrastructure Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5899c6b78ccd353</t>
+          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Core Infrastructure Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=192d7298c1dbe48c</t>
+          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C&amp;W Services</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e432297bb03d47</t>
+          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Glue, MLflow, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer, Dev Ops</t>
+          <t>Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, S3, EC2, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=475b5911e2c343f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e9b1416bfee140a4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cyber Security Engineer - Automation, Data Center &amp; Networking Security</t>
+          <t>APPLICATION DEVELOPER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Latitude AI</t>
+          <t>Atos</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,77 +1126,567 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d52ae75da259a3</t>
+          <t>https://www.indeed.com/viewjob?jk=13c211131b671ac7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Storage Platform Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Data Lake, CI/CD, Terraform, R, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist - Supply Chain</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Applied Machine Learning Engineer I</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Techtronic Industries Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9c3cc2c9562f4ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Applied Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Techtronic Industries Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6adeca2d2b4eda5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Onsite - Woodlawn, MD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Infoorigin Inc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Woodlawn, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, spaCy, CI/CD, Jenkins, Hadoop, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e67de3fb35e39800</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SCOR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, MySQL, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Entitlement I - Sr. Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bluematrix</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Kinesis, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45974b9c03dac7e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>bluematrix</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kinesis, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6eff3f3607854e4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Reporting Analyst (must have Sigma experience)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Coursera</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Redshift, Databricks, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8f628f5332cfef7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist, NA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48fd7a031e1ff74d</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI ENGINEER</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Atos</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Aurora, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4920dc6667911d73</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c770684f37ba8130</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI ENGINEER</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Atos</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Aurora, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Gemini, Kubernetes, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70ec6623e2130ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer, Quantum Systems &amp; Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Infleqtion</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb6a4ad1b1490d75</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MACH INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea782905b3d4a34b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MACH INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba7c95d148ae3357</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Techtronic Industries Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, CI/CD, Databricks, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-02.xlsx
+++ b/daily_matches/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence / Machine Learning Developer</t>
+          <t>AI/ML Data Scientist (GPSSC)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, spaCy, OpenCV, YOLO</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, S3, BigQuery, Data Lake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
+          <t>https://www.indeed.com/viewjob?jk=060ac516e5d04bc2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Java Backend Developer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, Kafka, Hadoop, PostgreSQL, MongoDB, Cassandra</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Dataflow, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cf49dceb0f513c</t>
+          <t>https://www.indeed.com/viewjob?jk=4285c04ca20cf636</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Git, Snowflake, Databricks, Kafka, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>RAG, S3, Glue, Redshift, Synapse, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
+          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full Stack Product Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Keras, MLflow, Docker, CI/CD</t>
+          <t>S3, FastAPI, Docker, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Polars, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b38b2d7dd112b433</t>
+          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer Technology</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Kinesis, CI/CD, Redshift, PySpark, Kafka, MySQL, NoSQL</t>
+          <t>RAG, S3, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Attain</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Dask</t>
+          <t>RAG, S3, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bc14828ef1e67f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Applied Growth, Monetization &amp; AI Engineer Vertical Search, Intelligence and Digital Publishing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Attain</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Dask</t>
+          <t>AI Engineer, PyTorch, XGBoost, LightGBM, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1988c96da6897747</t>
+          <t>https://www.indeed.com/viewjob?jk=b04fea50699d42a7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - Analytics</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, AKS, CI/CD, GitHub Actions, Git, Databricks, Tableau, Power BI</t>
+          <t>Generative AI, RAG, BigQuery, Dataflow, MLflow, Docker, Kubernetes, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
+          <t>https://www.indeed.com/viewjob?jk=510b1e334c4fe4f9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NoSQL Database Engineer || Onsite</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ukund</t>
+          <t>GXO Logistics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, GCP Vertex AI, FastAPI, Docker, Kubernetes, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9314bc9cfb51fe1b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>APPLICATION DEVELOPER</t>
+          <t>Java Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atos</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Git, BigQuery, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b7d6cdbfaa32a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c4d5515734cd07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>Senior Machine Learning Engineer- Generative AI (REMOTE)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, BigQuery, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8eb7066c5357ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=e1801adde79b2420</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Penguin Solutions</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, MLflow, Docker, Kubernetes, Terraform</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Apache Airflow, Terraform, Git, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999a52875fb68380</t>
+          <t>https://www.indeed.com/viewjob?jk=bb6a7c26a7dd7549</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Machine Learning Engineer, Forecasting</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Apella</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=25a3e98d88bcad06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>S3, EC2, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb849225e8b2c49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. AI-First Full Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Snowflake, Databricks, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=148fca9d00fe711c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
+          <t>https://www.indeed.com/viewjob?jk=d7549a5189ca5308</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Data Lake, MLflow, Snowflake, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Intern - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Gravie</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Git, Databricks, Python, SQL, R, Java</t>
+          <t>RAG, S3, Glue, Athena, CI/CD, Terraform, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9b1416bfee140a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>APPLICATION DEVELOPER</t>
+          <t>Senior Linux Systems Engineer - EDA Infrastructure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Atos</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13c211131b671ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=7742d0b26150948e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Software Engineer(Distributed Systems)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>RAG, S3, Data Lake, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
+          <t>https://www.indeed.com/viewjob?jk=9f467ec313d4cc07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer(Distributed Systems)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Snowflake, Kafka, Python, SQL, R</t>
+          <t>RAG, S3, Data Lake, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer I</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>Nestlé USA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, Snowflake, Databricks, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c3cc2c9562f4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e6aa688f7195c9f3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, SQL, R, Optimization</t>
+          <t>BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6adeca2d2b4eda5</t>
+          <t>https://www.indeed.com/viewjob?jk=af41ed2c88d54dca</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Onsite - Woodlawn, MD</t>
+          <t>Sr. Data Scientist (Forecasting)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Nestlé USA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, spaCy, CI/CD, Jenkins, Hadoop, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67de3fb35e39800</t>
+          <t>https://www.indeed.com/viewjob?jk=bd2368509716f86b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer</t>
+          <t>Applied AI Engineer – Equities &amp; Fixed Income Sales</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SCOR</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, MySQL, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb5334f52ca6546</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Entitlement I - Sr. Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kinesis, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45974b9c03dac7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b33e72ca723bb458</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III (Python/AWS)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kinesis, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eff3f3607854e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=004781402b66f4f8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Reporting Analyst (must have Sigma experience)</t>
+          <t>Senior Data Analyst / Informaticist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coursera</t>
+          <t>CenterWell</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Redshift, Databricks, Redshift, SQL, R, Scala</t>
+          <t>RAG, Copilot, Databricks, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f628f5332cfef7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8d753749f5ac8e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist, NA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Git, Snowflake, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd7a031e1ff74d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e72a54bf041cd9b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI ENGINEER</t>
+          <t>Software Development Engineer (US Federal)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Atos</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c770684f37ba8130</t>
+          <t>https://www.indeed.com/viewjob?jk=5966d48a80599b7f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI ENGINEER</t>
+          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Atos</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Gemini, Kubernetes, Terraform, Git, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ec6623e2130ece</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer, Quantum Systems &amp; Digital Engineering</t>
+          <t>Senior Software Test Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Infleqtion</t>
+          <t>oura</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Python, R, Scala, Optimization, Bayesian</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6a4ad1b1490d75</t>
+          <t>https://www.indeed.com/viewjob?jk=37ac446f088e4221</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Forward-Deployed Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MACH INDUSTRIES</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea782905b3d4a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=db5aa5a873d92078</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MACH INDUSTRIES</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7c95d148ae3357</t>
+          <t>https://www.indeed.com/viewjob?jk=8e73019eac2d5fea</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Distinguished Engineer, AI Applications</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,157 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, CI/CD, Databricks, Kafka, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, Azure ML, Snowflake, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3cc2ae90b2cb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Solution Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c29367938bda715b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Solution Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8880f249d806c24c</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Solution Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Baker Tilly Canada</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa66504dec0a5f5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer IV $100,000- $130,000 Missoula/Hybrid/Remote</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ELM Utility Services</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Missoula, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1d3a6e613433e79</t>
         </is>
       </c>
     </row>
